--- a/Backend/srvdata/barcode.xlsx
+++ b/Backend/srvdata/barcode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="79">
   <si>
     <t>EPL</t>
+  </si>
+  <si>
+    <t>TSPL</t>
   </si>
   <si>
     <t>EAN13</t>
@@ -1315,387 +1318,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
     <col min="3" max="3" width="28.2166666666667" style="8" customWidth="1"/>
     <col min="4" max="4" width="9.10833333333333" customWidth="1"/>
     <col min="5" max="5" width="40.2166666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="D1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" spans="1:6">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5" spans="1:5">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:5">
+    </row>
+    <row r="5" ht="28.5" spans="1:6">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5" spans="1:5">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>7</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:5">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:6">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:6">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="28.5" spans="1:6">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="28.5" spans="1:5">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="42.75" spans="1:6">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" spans="1:5">
-      <c r="A10" t="s">
+      <c r="E10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>19</v>
       </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
       <c r="E14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" ht="28.5" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="28.5" spans="1:6">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" ht="28.5" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F18">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="28.5" spans="1:6">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
         <v>14</v>
       </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
       <c r="E19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" ht="28.5" spans="1:6">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" ht="28.5" spans="1:5">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
       <c r="E20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" ht="42.75" spans="1:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="42.75" spans="1:6">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1717,10 +1751,10 @@
   <sheetData>
     <row r="1" ht="17.25" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
@@ -1728,15 +1762,15 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:2">
@@ -1744,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:2">
@@ -1752,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:2">
@@ -1760,79 +1794,79 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:2">
       <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:2">
       <c r="A11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>2</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:2">
@@ -1840,103 +1874,103 @@
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="26.25" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="26.25" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="15" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" ht="15" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:2">
       <c r="A28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" ht="15"/>

--- a/Backend/srvdata/barcode.xlsx
+++ b/Backend/srvdata/barcode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="22800" windowHeight="8790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="85">
   <si>
     <t>EPL</t>
   </si>
@@ -36,6 +36,9 @@
     <t>TSPL</t>
   </si>
   <si>
+    <t>EZPL</t>
+  </si>
+  <si>
     <t>EAN13</t>
   </si>
   <si>
@@ -45,6 +48,9 @@
     <t>EAN13条码</t>
   </si>
   <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>E30_SWEDEN</t>
   </si>
   <si>
@@ -60,6 +66,9 @@
     <t>Code 128 auto A,B,C modes</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>CODE128</t>
   </si>
   <si>
@@ -96,6 +105,9 @@
     <t>EAN8条码</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>UPCAITF14</t>
   </si>
   <si>
@@ -138,6 +150,9 @@
     <t>CODE39条码</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>E18</t>
   </si>
   <si>
@@ -156,9 +171,15 @@
     <t>UE0</t>
   </si>
   <si>
+    <t>K</t>
+  </si>
+  <si>
     <t>UPCA</t>
   </si>
   <si>
+    <t>H</t>
+  </si>
+  <si>
     <t>String</t>
   </si>
   <si>
@@ -175,9 +196,6 @@
   </si>
   <si>
     <t>Code 93</t>
-  </si>
-  <si>
-    <t>K</t>
   </si>
   <si>
     <t>Codabar</t>
@@ -1318,8 +1336,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
@@ -1329,407 +1347,443 @@
     <col min="6" max="6" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" spans="1:7">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5" spans="1:6">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:6">
+    </row>
+    <row r="5" ht="28.5" spans="1:7">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>128</v>
       </c>
-    </row>
-    <row r="6" ht="28.5" spans="1:6">
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>8</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>128</v>
       </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:6">
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:6">
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="28.5" spans="1:7">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" ht="28.5" spans="1:6">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="42.75" spans="1:7">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
       <c r="E10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>22</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" ht="28.5" spans="1:6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="28.5" spans="1:7">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F18">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" ht="28.5" spans="1:6">
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" ht="28.5" spans="1:7">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" ht="28.5" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" ht="28.5" spans="1:7">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" ht="42.75" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="42.75" spans="1:7">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1751,10 +1805,10 @@
   <sheetData>
     <row r="1" ht="17.25" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
@@ -1762,15 +1816,15 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:2">
@@ -1778,7 +1832,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:2">
@@ -1786,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:2">
@@ -1794,79 +1848,79 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:2">
       <c r="A11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:2">
@@ -1874,103 +1928,103 @@
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="26.25" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="26.25" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" ht="15" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" ht="15" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:2">
       <c r="A28" s="6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" ht="15"/>
